--- a/dc2_milk_run_routes.xlsx
+++ b/dc2_milk_run_routes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,14 +493,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DPI70317 -&gt; DPI66175 -&gt; DPI64476 -&gt; DPI66659 -&gt; DPI70100 -&gt; DPI63920 -&gt; DPI66528 -&gt; DPI64255 -&gt; DPI64409</t>
+          <t>DPI66387 -&gt; DPI70316 -&gt; DPI64216 -&gt; DFT80088 -&gt; DPI64413 -&gt; DPI70096 -&gt; DPI64037 -&gt; DPI66172 -&gt; DPI64057 -&gt; DPI63802 -&gt; DPI66051 -&gt; DPI64169 -&gt; DPI66715</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="F2" t="n">
         <v>1613</v>
@@ -509,13 +509,13 @@
         <v>980</v>
       </c>
       <c r="H2" t="n">
-        <v>99.48999999999999</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>572.15</v>
+        <v>916.47</v>
       </c>
       <c r="J2" t="n">
-        <v>1176641.32</v>
+        <v>1289612.88</v>
       </c>
     </row>
     <row r="3">
@@ -531,14 +531,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DPI67198 -&gt; DPI64692 -&gt; DPI64303 -&gt; DPI67128 -&gt; DPI64378 -&gt; DPI66421 -&gt; DPI63822</t>
+          <t>DPI66658 -&gt; DPI67148 -&gt; DPI64742 -&gt; DPI63976 -&gt; DPI70296 -&gt; DPI67180 -&gt; DPI64634 -&gt; DPI67224 -&gt; DPI66209</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="F3" t="n">
         <v>1613</v>
@@ -547,13 +547,13 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>484.71</v>
+        <v>983.55</v>
       </c>
       <c r="J3" t="n">
-        <v>1147952.65</v>
+        <v>1311624.09</v>
       </c>
     </row>
     <row r="4">
@@ -569,14 +569,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DPI64104 -&gt; DPI66646 -&gt; DPI70041 -&gt; DPI67024 -&gt; DPI64288 -&gt; DPI64352 -&gt; DPI67031 -&gt; DPI66264</t>
+          <t>DPI70109 -&gt; DPI66129 -&gt; DPI64495 -&gt; DFT80080 -&gt; DPI64548 -&gt; DPI70107 -&gt; DPI70214 -&gt; DPI66634</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>931</v>
+        <v>824</v>
       </c>
       <c r="F4" t="n">
         <v>1613</v>
@@ -585,13 +585,13 @@
         <v>980</v>
       </c>
       <c r="H4" t="n">
-        <v>95</v>
+        <v>84.08</v>
       </c>
       <c r="I4" t="n">
-        <v>920.58</v>
+        <v>1399.26</v>
       </c>
       <c r="J4" t="n">
-        <v>1290962.38</v>
+        <v>1448016.3</v>
       </c>
     </row>
     <row r="5">
@@ -607,14 +607,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DFT80081 -&gt; DFT80034 -&gt; DPI66508 -&gt; DPI66229 -&gt; DPI63817 -&gt; DPI64511 -&gt; DPI63895 -&gt; DPI66335 -&gt; DPI70002 -&gt; DPI70106</t>
+          <t>DPI64052 -&gt; DPI67187 -&gt; DPI64666 -&gt; DPI70190 -&gt; DPI70253 -&gt; DPI64056 -&gt; DPI67074 -&gt; DPI64628 -&gt; DPI64119 -&gt; DPI66636</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>901</v>
+        <v>956</v>
       </c>
       <c r="F5" t="n">
         <v>1613</v>
@@ -623,13 +623,13 @@
         <v>980</v>
       </c>
       <c r="H5" t="n">
-        <v>91.94</v>
+        <v>97.55</v>
       </c>
       <c r="I5" t="n">
-        <v>600.4400000000001</v>
+        <v>1065.26</v>
       </c>
       <c r="J5" t="n">
-        <v>1185922.8</v>
+        <v>1338431.88</v>
       </c>
     </row>
     <row r="6">
@@ -645,14 +645,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPI70197 -&gt; DPI63847 -&gt; DPI66144 -&gt; DPI70273 -&gt; DPI70179 -&gt; DPI70302 -&gt; DFT80087 -&gt; DPI64559 -&gt; DPI66327 -&gt; DPI64484 -&gt; DPI66092 -&gt; DFT80066</t>
+          <t>DPI66597 -&gt; DPI66373 -&gt; DPI66154 -&gt; DPI66153 -&gt; DPI67072 -&gt; DPI66449 -&gt; DPI64431 -&gt; DPI64196 -&gt; DPI66221</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>946</v>
+        <v>957</v>
       </c>
       <c r="F6" t="n">
         <v>1613</v>
@@ -661,13 +661,13 @@
         <v>980</v>
       </c>
       <c r="H6" t="n">
-        <v>96.53</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>549.16</v>
+        <v>534.65</v>
       </c>
       <c r="J6" t="n">
-        <v>1169098.19</v>
+        <v>1164337.75</v>
       </c>
     </row>
     <row r="7">
@@ -683,14 +683,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPI64639 -&gt; DPI64044 -&gt; DPI63993 -&gt; DPI66460 -&gt; DPI64176 -&gt; DPI64234 -&gt; DPI66572 -&gt; DPI64149 -&gt; DPI70038 -&gt; DPI70073 -&gt; DPI66734 -&gt; DPI64236 -&gt; DPI66684</t>
+          <t>DPI66069 -&gt; DPI64039 -&gt; DPI66289 -&gt; DPI66203 -&gt; DPI66574 -&gt; DPI66078 -&gt; DPI64433 -&gt; DPI64480</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>945</v>
+        <v>969</v>
       </c>
       <c r="F7" t="n">
         <v>1613</v>
@@ -699,13 +699,13 @@
         <v>980</v>
       </c>
       <c r="H7" t="n">
-        <v>96.43000000000001</v>
+        <v>98.88</v>
       </c>
       <c r="I7" t="n">
-        <v>1342.06</v>
+        <v>976.47</v>
       </c>
       <c r="J7" t="n">
-        <v>1429248.42</v>
+        <v>1309299.2</v>
       </c>
     </row>
     <row r="8">
@@ -721,14 +721,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPI64651 -&gt; DPI66262 -&gt; DPI64166 -&gt; DPI66384 -&gt; DPI64392 -&gt; DPI66408 -&gt; DPI64624 -&gt; DPI66102</t>
+          <t>DPI64436 -&gt; DPI64456 -&gt; DPI66946 -&gt; DPI64136 -&gt; DPI67121 -&gt; DPI66039 -&gt; DPI66307 -&gt; DPI64638 -&gt; DPI63958</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>943</v>
+        <v>961</v>
       </c>
       <c r="F8" t="n">
         <v>1613</v>
@@ -737,13 +737,13 @@
         <v>980</v>
       </c>
       <c r="H8" t="n">
-        <v>96.22</v>
+        <v>98.06</v>
       </c>
       <c r="I8" t="n">
-        <v>930.85</v>
+        <v>919.02</v>
       </c>
       <c r="J8" t="n">
-        <v>1294330.84</v>
+        <v>1290449.92</v>
       </c>
     </row>
     <row r="9">
@@ -759,14 +759,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DPI64696 -&gt; DPI66692 -&gt; DPI64323 -&gt; DPI66618 -&gt; DPI64746 -&gt; DPI64179 -&gt; DPI66900</t>
+          <t>DPI66179 -&gt; DPI64218 -&gt; DPI64301 -&gt; DPI70255 -&gt; DPI66645 -&gt; DPI64244 -&gt; DPI66128 -&gt; DPI64094 -&gt; DPI70142</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>941</v>
+        <v>962</v>
       </c>
       <c r="F9" t="n">
         <v>1613</v>
@@ -775,13 +775,13 @@
         <v>980</v>
       </c>
       <c r="H9" t="n">
-        <v>96.02</v>
+        <v>98.16</v>
       </c>
       <c r="I9" t="n">
-        <v>1025.45</v>
+        <v>613.0599999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>1325369.72</v>
+        <v>1190066.08</v>
       </c>
     </row>
     <row r="10">
@@ -797,29 +797,143 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DPI64758 -&gt; DPI64647 -&gt; DPI64032 -&gt; DPI66402 -&gt; DPI70120 -&gt; DPI64502 -&gt; DPI66263 -&gt; DPI64665 -&gt; DPI64273</t>
+          <t>DPI70009 -&gt; DPI63827 -&gt; DPI66313 -&gt; DPI66576 -&gt; DPI64592 -&gt; DPI63919 -&gt; DPI66679 -&gt; DPI70047 -&gt; DPI66923 -&gt; DFT80078</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>965</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1613</v>
+      </c>
+      <c r="G10" t="n">
+        <v>980</v>
+      </c>
+      <c r="H10" t="n">
+        <v>98.47</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1113.51</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1354263.26</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DPI70081 -&gt; DPI64624 -&gt; DPI66102 -&gt; DPI64166 -&gt; DPI66384 -&gt; DPI66408 -&gt; DPI64392 -&gt; DPI66618 -&gt; DPI66653</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>9</v>
       </c>
-      <c r="E10" t="n">
-        <v>956</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1613</v>
-      </c>
-      <c r="G10" t="n">
-        <v>980</v>
-      </c>
-      <c r="H10" t="n">
-        <v>97.55</v>
-      </c>
-      <c r="I10" t="n">
-        <v>600.86</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1186061.97</v>
+      <c r="E11" t="n">
+        <v>979</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1613</v>
+      </c>
+      <c r="G11" t="n">
+        <v>980</v>
+      </c>
+      <c r="H11" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1073.08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1340998.31</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DFT80077 -&gt; DPI70105 -&gt; DPI63915 -&gt; DPI64724 -&gt; DPI64297 -&gt; DPI67178 -&gt; DPI66742 -&gt; DPI66067 -&gt; DPI70213</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>965</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1613</v>
+      </c>
+      <c r="G12" t="n">
+        <v>980</v>
+      </c>
+      <c r="H12" t="n">
+        <v>98.47</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1036.61</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1329031.43</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DPI64450 -&gt; DPI64686 -&gt; DPI66339 -&gt; DPI66590 -&gt; DFT80044 -&gt; DPI66096 -&gt; DPI64018 -&gt; DPI70229 -&gt; DPI66736</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>966</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1613</v>
+      </c>
+      <c r="G13" t="n">
+        <v>980</v>
+      </c>
+      <c r="H13" t="n">
+        <v>98.56999999999999</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1341.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1429098.01</v>
       </c>
     </row>
   </sheetData>

--- a/dc2_milk_run_routes.xlsx
+++ b/dc2_milk_run_routes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,14 +493,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DPI66387 -&gt; DPI70316 -&gt; DPI64216 -&gt; DFT80088 -&gt; DPI64413 -&gt; DPI70096 -&gt; DPI64037 -&gt; DPI66172 -&gt; DPI64057 -&gt; DPI63802 -&gt; DPI66051 -&gt; DPI64169 -&gt; DPI66715</t>
+          <t>DPI64218 -&gt; DPI66289 -&gt; DPI64039 -&gt; DPI66069 -&gt; DPI70255 -&gt; DPI66645 -&gt; DPI64413 -&gt; DPI64244 -&gt; DFT80088 -&gt; DPI64216 -&gt; DPI70316</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>972</v>
+        <v>926</v>
       </c>
       <c r="F2" t="n">
         <v>1613</v>
@@ -509,13 +509,13 @@
         <v>980</v>
       </c>
       <c r="H2" t="n">
-        <v>99.18000000000001</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>916.47</v>
+        <v>595.22</v>
       </c>
       <c r="J2" t="n">
-        <v>1289612.88</v>
+        <v>1184213.11</v>
       </c>
     </row>
     <row r="3">
@@ -607,14 +607,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DPI64052 -&gt; DPI67187 -&gt; DPI64666 -&gt; DPI70190 -&gt; DPI70253 -&gt; DPI64056 -&gt; DPI67074 -&gt; DPI64628 -&gt; DPI64119 -&gt; DPI66636</t>
+          <t>DPI64052 -&gt; DPI66179 -&gt; DPI66597 -&gt; DPI63958 -&gt; DPI66039 -&gt; DPI66307 -&gt; DPI64638</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>956</v>
+        <v>865</v>
       </c>
       <c r="F5" t="n">
         <v>1613</v>
@@ -623,13 +623,13 @@
         <v>980</v>
       </c>
       <c r="H5" t="n">
-        <v>97.55</v>
+        <v>88.27</v>
       </c>
       <c r="I5" t="n">
-        <v>1065.26</v>
+        <v>204.96</v>
       </c>
       <c r="J5" t="n">
-        <v>1338431.88</v>
+        <v>1056168.82</v>
       </c>
     </row>
     <row r="6">
@@ -645,14 +645,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPI66597 -&gt; DPI66373 -&gt; DPI66154 -&gt; DPI66153 -&gt; DPI67072 -&gt; DPI66449 -&gt; DPI64431 -&gt; DPI64196 -&gt; DPI66221</t>
+          <t>DPI70009 -&gt; DPI63827 -&gt; DPI66313 -&gt; DPI66576 -&gt; DPI64592 -&gt; DPI63919 -&gt; DPI66679 -&gt; DPI70047</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>957</v>
+        <v>854</v>
       </c>
       <c r="F6" t="n">
         <v>1613</v>
@@ -661,13 +661,13 @@
         <v>980</v>
       </c>
       <c r="H6" t="n">
-        <v>97.65000000000001</v>
+        <v>87.14</v>
       </c>
       <c r="I6" t="n">
-        <v>534.65</v>
+        <v>708.0700000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1164337.75</v>
+        <v>1221236.44</v>
       </c>
     </row>
     <row r="7">
@@ -683,14 +683,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPI66069 -&gt; DPI64039 -&gt; DPI66289 -&gt; DPI66203 -&gt; DPI66574 -&gt; DPI66078 -&gt; DPI64433 -&gt; DPI64480</t>
+          <t>DPI64094 -&gt; DPI66128 -&gt; DPI70096 -&gt; DPI64037 -&gt; DPI66172 -&gt; DPI64057 -&gt; DPI63802 -&gt; DPI66051 -&gt; DPI64169 -&gt; DPI66715</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>969</v>
+        <v>925</v>
       </c>
       <c r="F7" t="n">
         <v>1613</v>
@@ -699,13 +699,13 @@
         <v>980</v>
       </c>
       <c r="H7" t="n">
-        <v>98.88</v>
+        <v>94.39</v>
       </c>
       <c r="I7" t="n">
-        <v>976.47</v>
+        <v>920.26</v>
       </c>
       <c r="J7" t="n">
-        <v>1309299.2</v>
+        <v>1290856.8</v>
       </c>
     </row>
     <row r="8">
@@ -721,14 +721,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPI64436 -&gt; DPI64456 -&gt; DPI66946 -&gt; DPI64136 -&gt; DPI67121 -&gt; DPI66039 -&gt; DPI66307 -&gt; DPI64638 -&gt; DPI63958</t>
+          <t>DPI66653 -&gt; DPI66449 -&gt; DPI67072 -&gt; DPI66153 -&gt; DPI70081 -&gt; DPI66154 -&gt; DPI66373 -&gt; DPI66221</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>961</v>
+        <v>871</v>
       </c>
       <c r="F8" t="n">
         <v>1613</v>
@@ -737,13 +737,13 @@
         <v>980</v>
       </c>
       <c r="H8" t="n">
-        <v>98.06</v>
+        <v>88.88</v>
       </c>
       <c r="I8" t="n">
-        <v>919.02</v>
+        <v>426.58</v>
       </c>
       <c r="J8" t="n">
-        <v>1290449.92</v>
+        <v>1128881.93</v>
       </c>
     </row>
     <row r="9">
@@ -759,14 +759,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DPI66179 -&gt; DPI64218 -&gt; DPI64301 -&gt; DPI70255 -&gt; DPI66645 -&gt; DPI64244 -&gt; DPI66128 -&gt; DPI64094 -&gt; DPI70142</t>
+          <t>DPI64480 -&gt; DPI66078 -&gt; DPI64433 -&gt; DPI67187 -&gt; DPI70105 -&gt; DPI64436 -&gt; DPI64456 -&gt; DPI66946 -&gt; DPI66574</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="F9" t="n">
         <v>1613</v>
@@ -775,13 +775,13 @@
         <v>980</v>
       </c>
       <c r="H9" t="n">
-        <v>98.16</v>
+        <v>98.27</v>
       </c>
       <c r="I9" t="n">
-        <v>613.0599999999999</v>
+        <v>874.7</v>
       </c>
       <c r="J9" t="n">
-        <v>1190066.08</v>
+        <v>1275910.65</v>
       </c>
     </row>
     <row r="10">
@@ -797,14 +797,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DPI70009 -&gt; DPI63827 -&gt; DPI66313 -&gt; DPI66576 -&gt; DPI64592 -&gt; DPI63919 -&gt; DPI66679 -&gt; DPI70047 -&gt; DPI66923 -&gt; DFT80078</t>
+          <t>DPI67121 -&gt; DPI64450 -&gt; DPI64686 -&gt; DPI66203 -&gt; DPI64301 -&gt; DFT80044 -&gt; DPI66590 -&gt; DPI66339 -&gt; DPI66387</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>965</v>
+        <v>957</v>
       </c>
       <c r="F10" t="n">
         <v>1613</v>
@@ -813,13 +813,13 @@
         <v>980</v>
       </c>
       <c r="H10" t="n">
-        <v>98.47</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>1113.51</v>
+        <v>222.61</v>
       </c>
       <c r="J10" t="n">
-        <v>1354263.26</v>
+        <v>1061956.75</v>
       </c>
     </row>
     <row r="11">
@@ -835,14 +835,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DPI70081 -&gt; DPI64624 -&gt; DPI66102 -&gt; DPI64166 -&gt; DPI66384 -&gt; DPI66408 -&gt; DPI64392 -&gt; DPI66618 -&gt; DPI66653</t>
+          <t>DPI70142 -&gt; DPI66742 -&gt; DPI63915 -&gt; DPI64724 -&gt; DPI67178 -&gt; DPI64297 -&gt; DPI66067 -&gt; DPI70213 -&gt; DPI64136</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="F11" t="n">
         <v>1613</v>
@@ -851,13 +851,13 @@
         <v>980</v>
       </c>
       <c r="H11" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1073.08</v>
+        <v>855.61</v>
       </c>
       <c r="J11" t="n">
-        <v>1340998.31</v>
+        <v>1269644.42</v>
       </c>
     </row>
     <row r="12">
@@ -873,29 +873,29 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DFT80077 -&gt; DPI70105 -&gt; DPI63915 -&gt; DPI64724 -&gt; DPI64297 -&gt; DPI67178 -&gt; DPI66742 -&gt; DPI66067 -&gt; DPI70213</t>
+          <t>DPI66736 -&gt; DPI70229 -&gt; DPI64018 -&gt; DPI66096</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>965</v>
+        <v>520</v>
       </c>
       <c r="F12" t="n">
-        <v>1613</v>
+        <v>1109</v>
       </c>
       <c r="G12" t="n">
-        <v>980</v>
+        <v>660</v>
       </c>
       <c r="H12" t="n">
-        <v>98.47</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>1036.61</v>
+        <v>1183.99</v>
       </c>
       <c r="J12" t="n">
-        <v>1329031.43</v>
+        <v>1198199.77</v>
       </c>
     </row>
     <row r="13">
@@ -911,14 +911,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DPI64450 -&gt; DPI64686 -&gt; DPI66339 -&gt; DPI66590 -&gt; DFT80044 -&gt; DPI66096 -&gt; DPI64018 -&gt; DPI70229 -&gt; DPI66736</t>
+          <t>DPI64196 -&gt; DPI64624 -&gt; DPI66102 -&gt; DPI64166 -&gt; DPI66384 -&gt; DPI66408 -&gt; DPI64392 -&gt; DPI66618 -&gt; DPI64431</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="F13" t="n">
         <v>1613</v>
@@ -927,13 +927,51 @@
         <v>980</v>
       </c>
       <c r="H13" t="n">
-        <v>98.56999999999999</v>
+        <v>99.39</v>
       </c>
       <c r="I13" t="n">
-        <v>1341.6</v>
+        <v>1068.39</v>
       </c>
       <c r="J13" t="n">
-        <v>1429098.01</v>
+        <v>1339460.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DPI66923 -&gt; DFT80077 -&gt; DPI66636 -&gt; DPI64666 -&gt; DPI70190 -&gt; DPI70253 -&gt; DPI64056 -&gt; DPI67074 -&gt; DPI64628 -&gt; DPI64119 -&gt; DFT80078</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E14" t="n">
+        <v>819</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1613</v>
+      </c>
+      <c r="G14" t="n">
+        <v>980</v>
+      </c>
+      <c r="H14" t="n">
+        <v>83.56999999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>939.01</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1297009.88</v>
       </c>
     </row>
   </sheetData>

--- a/dc2_milk_run_routes.xlsx
+++ b/dc2_milk_run_routes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,14 +493,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DPI64218 -&gt; DPI66289 -&gt; DPI64039 -&gt; DPI66069 -&gt; DPI70255 -&gt; DPI66645 -&gt; DPI64413 -&gt; DPI64244 -&gt; DFT80088 -&gt; DPI64216 -&gt; DPI70316</t>
+          <t>DPI66387 -&gt; DPI70316 -&gt; DPI64216 -&gt; DFT80088 -&gt; DPI64413 -&gt; DPI70096 -&gt; DPI64037 -&gt; DPI66172 -&gt; DPI64057 -&gt; DPI63802 -&gt; DPI66051 -&gt; DPI64169 -&gt; DPI66715</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>926</v>
+        <v>972</v>
       </c>
       <c r="F2" t="n">
         <v>1613</v>
@@ -509,13 +509,13 @@
         <v>980</v>
       </c>
       <c r="H2" t="n">
-        <v>94.48999999999999</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>595.22</v>
+        <v>916.47</v>
       </c>
       <c r="J2" t="n">
-        <v>1184213.11</v>
+        <v>1289612.88</v>
       </c>
     </row>
     <row r="3">
@@ -607,14 +607,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DPI64052 -&gt; DPI66179 -&gt; DPI66597 -&gt; DPI63958 -&gt; DPI66039 -&gt; DPI66307 -&gt; DPI64638</t>
+          <t>DPI64052 -&gt; DPI67187 -&gt; DPI64666 -&gt; DPI70190 -&gt; DPI70253 -&gt; DPI64056 -&gt; DPI67074 -&gt; DPI64628 -&gt; DPI64119 -&gt; DPI66636</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>865</v>
+        <v>956</v>
       </c>
       <c r="F5" t="n">
         <v>1613</v>
@@ -623,13 +623,13 @@
         <v>980</v>
       </c>
       <c r="H5" t="n">
-        <v>88.27</v>
+        <v>97.55</v>
       </c>
       <c r="I5" t="n">
-        <v>204.96</v>
+        <v>1065.26</v>
       </c>
       <c r="J5" t="n">
-        <v>1056168.82</v>
+        <v>1338431.88</v>
       </c>
     </row>
     <row r="6">
@@ -645,14 +645,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPI70009 -&gt; DPI63827 -&gt; DPI66313 -&gt; DPI66576 -&gt; DPI64592 -&gt; DPI63919 -&gt; DPI66679 -&gt; DPI70047</t>
+          <t>DPI64431 -&gt; DPI66449 -&gt; DPI67072 -&gt; DPI66153 -&gt; DPI66154 -&gt; DPI66373 -&gt; DPI64196 -&gt; DPI66221 -&gt; DPI66597</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>854</v>
+        <v>957</v>
       </c>
       <c r="F6" t="n">
         <v>1613</v>
@@ -661,13 +661,13 @@
         <v>980</v>
       </c>
       <c r="H6" t="n">
-        <v>87.14</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>708.0700000000001</v>
+        <v>529.26</v>
       </c>
       <c r="J6" t="n">
-        <v>1221236.44</v>
+        <v>1162570.49</v>
       </c>
     </row>
     <row r="7">
@@ -683,14 +683,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPI64094 -&gt; DPI66128 -&gt; DPI70096 -&gt; DPI64037 -&gt; DPI66172 -&gt; DPI64057 -&gt; DPI63802 -&gt; DPI66051 -&gt; DPI64169 -&gt; DPI66715</t>
+          <t>DPI66069 -&gt; DPI64039 -&gt; DPI66289 -&gt; DPI66203 -&gt; DPI66574 -&gt; DPI66078 -&gt; DPI64433 -&gt; DPI64480</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>925</v>
+        <v>969</v>
       </c>
       <c r="F7" t="n">
         <v>1613</v>
@@ -699,13 +699,13 @@
         <v>980</v>
       </c>
       <c r="H7" t="n">
-        <v>94.39</v>
+        <v>98.88</v>
       </c>
       <c r="I7" t="n">
-        <v>920.26</v>
+        <v>976.47</v>
       </c>
       <c r="J7" t="n">
-        <v>1290856.8</v>
+        <v>1309299.2</v>
       </c>
     </row>
     <row r="8">
@@ -721,14 +721,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPI66653 -&gt; DPI66449 -&gt; DPI67072 -&gt; DPI66153 -&gt; DPI70081 -&gt; DPI66154 -&gt; DPI66373 -&gt; DPI66221</t>
+          <t>DPI64436 -&gt; DPI64456 -&gt; DPI66946 -&gt; DPI64136 -&gt; DPI67121 -&gt; DPI66039 -&gt; DPI66307 -&gt; DPI64638 -&gt; DPI63958</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>871</v>
+        <v>961</v>
       </c>
       <c r="F8" t="n">
         <v>1613</v>
@@ -737,13 +737,13 @@
         <v>980</v>
       </c>
       <c r="H8" t="n">
-        <v>88.88</v>
+        <v>98.06</v>
       </c>
       <c r="I8" t="n">
-        <v>426.58</v>
+        <v>919.02</v>
       </c>
       <c r="J8" t="n">
-        <v>1128881.93</v>
+        <v>1290449.92</v>
       </c>
     </row>
     <row r="9">
@@ -759,14 +759,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DPI64480 -&gt; DPI66078 -&gt; DPI64433 -&gt; DPI67187 -&gt; DPI70105 -&gt; DPI64436 -&gt; DPI64456 -&gt; DPI66946 -&gt; DPI66574</t>
+          <t>DPI66179 -&gt; DPI64218 -&gt; DPI64301 -&gt; DPI70255 -&gt; DPI66645 -&gt; DPI64244 -&gt; DPI66128 -&gt; DPI64094 -&gt; DPI70142</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="F9" t="n">
         <v>1613</v>
@@ -775,13 +775,13 @@
         <v>980</v>
       </c>
       <c r="H9" t="n">
-        <v>98.27</v>
+        <v>98.16</v>
       </c>
       <c r="I9" t="n">
-        <v>874.7</v>
+        <v>613.0599999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>1275910.65</v>
+        <v>1190066.08</v>
       </c>
     </row>
     <row r="10">
@@ -797,14 +797,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DPI67121 -&gt; DPI64450 -&gt; DPI64686 -&gt; DPI66203 -&gt; DPI64301 -&gt; DFT80044 -&gt; DPI66590 -&gt; DPI66339 -&gt; DPI66387</t>
+          <t>DPI70009 -&gt; DPI63827 -&gt; DPI66313 -&gt; DPI66576 -&gt; DPI64592 -&gt; DPI63919 -&gt; DPI66679 -&gt; DPI70047 -&gt; DPI66923 -&gt; DFT80078</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="F10" t="n">
         <v>1613</v>
@@ -813,13 +813,13 @@
         <v>980</v>
       </c>
       <c r="H10" t="n">
-        <v>97.65000000000001</v>
+        <v>98.47</v>
       </c>
       <c r="I10" t="n">
-        <v>222.61</v>
+        <v>1113.51</v>
       </c>
       <c r="J10" t="n">
-        <v>1061956.75</v>
+        <v>1354263.26</v>
       </c>
     </row>
     <row r="11">
@@ -835,14 +835,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DPI70142 -&gt; DPI66742 -&gt; DPI63915 -&gt; DPI64724 -&gt; DPI67178 -&gt; DPI64297 -&gt; DPI66067 -&gt; DPI70213 -&gt; DPI64136</t>
+          <t>DPI70081 -&gt; DPI64624 -&gt; DPI66102 -&gt; DPI64166 -&gt; DPI66384 -&gt; DPI66408 -&gt; DPI64392 -&gt; DPI66618 -&gt; DPI66653</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="F11" t="n">
         <v>1613</v>
@@ -851,13 +851,13 @@
         <v>980</v>
       </c>
       <c r="H11" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>855.61</v>
+        <v>1073.08</v>
       </c>
       <c r="J11" t="n">
-        <v>1269644.42</v>
+        <v>1340998.31</v>
       </c>
     </row>
     <row r="12">
@@ -873,29 +873,29 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DPI66736 -&gt; DPI70229 -&gt; DPI64018 -&gt; DPI66096</t>
+          <t>DPI67178 -&gt; DPI64297 -&gt; DPI63915 -&gt; DPI64724 -&gt; DPI66742 -&gt; DPI66067 -&gt; DPI70213 -&gt; DPI70105 -&gt; DFT80077</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>520</v>
+        <v>965</v>
       </c>
       <c r="F12" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="G12" t="n">
-        <v>660</v>
+        <v>980</v>
       </c>
       <c r="H12" t="n">
-        <v>78.79000000000001</v>
+        <v>98.47</v>
       </c>
       <c r="I12" t="n">
-        <v>1183.99</v>
+        <v>1036.17</v>
       </c>
       <c r="J12" t="n">
-        <v>1198199.77</v>
+        <v>1328887.68</v>
       </c>
     </row>
     <row r="13">
@@ -911,14 +911,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DPI64196 -&gt; DPI64624 -&gt; DPI66102 -&gt; DPI64166 -&gt; DPI66384 -&gt; DPI66408 -&gt; DPI64392 -&gt; DPI66618 -&gt; DPI64431</t>
+          <t>DPI64450 -&gt; DPI64686 -&gt; DPI66339 -&gt; DPI66590 -&gt; DFT80044 -&gt; DPI66096 -&gt; DPI64018 -&gt; DPI70229 -&gt; DPI66736</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="F13" t="n">
         <v>1613</v>
@@ -927,51 +927,13 @@
         <v>980</v>
       </c>
       <c r="H13" t="n">
-        <v>99.39</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>1068.39</v>
+        <v>1341.6</v>
       </c>
       <c r="J13" t="n">
-        <v>1339460.3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>R13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>DC_2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>DPI66923 -&gt; DFT80077 -&gt; DPI66636 -&gt; DPI64666 -&gt; DPI70190 -&gt; DPI70253 -&gt; DPI64056 -&gt; DPI67074 -&gt; DPI64628 -&gt; DPI64119 -&gt; DFT80078</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11</v>
-      </c>
-      <c r="E14" t="n">
-        <v>819</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1613</v>
-      </c>
-      <c r="G14" t="n">
-        <v>980</v>
-      </c>
-      <c r="H14" t="n">
-        <v>83.56999999999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>939.01</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1297009.88</v>
+        <v>1429098.01</v>
       </c>
     </row>
   </sheetData>

--- a/dc2_milk_run_routes.xlsx
+++ b/dc2_milk_run_routes.xlsx
@@ -515,7 +515,7 @@
         <v>916.47</v>
       </c>
       <c r="J2" t="n">
-        <v>1289612.88</v>
+        <v>399584.88</v>
       </c>
     </row>
     <row r="3">
@@ -553,7 +553,7 @@
         <v>983.55</v>
       </c>
       <c r="J3" t="n">
-        <v>1311624.09</v>
+        <v>421596.09</v>
       </c>
     </row>
     <row r="4">
@@ -591,7 +591,7 @@
         <v>1399.26</v>
       </c>
       <c r="J4" t="n">
-        <v>1448016.3</v>
+        <v>557988.3</v>
       </c>
     </row>
     <row r="5">
@@ -629,7 +629,7 @@
         <v>1065.26</v>
       </c>
       <c r="J5" t="n">
-        <v>1338431.88</v>
+        <v>448403.88</v>
       </c>
     </row>
     <row r="6">
@@ -667,7 +667,7 @@
         <v>529.26</v>
       </c>
       <c r="J6" t="n">
-        <v>1162570.49</v>
+        <v>272542.49</v>
       </c>
     </row>
     <row r="7">
@@ -705,7 +705,7 @@
         <v>976.47</v>
       </c>
       <c r="J7" t="n">
-        <v>1309299.2</v>
+        <v>419271.2</v>
       </c>
     </row>
     <row r="8">
@@ -743,7 +743,7 @@
         <v>919.02</v>
       </c>
       <c r="J8" t="n">
-        <v>1290449.92</v>
+        <v>400421.92</v>
       </c>
     </row>
     <row r="9">
@@ -781,7 +781,7 @@
         <v>613.0599999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>1190066.08</v>
+        <v>300038.08</v>
       </c>
     </row>
     <row r="10">
@@ -819,7 +819,7 @@
         <v>1113.51</v>
       </c>
       <c r="J10" t="n">
-        <v>1354263.26</v>
+        <v>464235.26</v>
       </c>
     </row>
     <row r="11">
@@ -857,7 +857,7 @@
         <v>1073.08</v>
       </c>
       <c r="J11" t="n">
-        <v>1340998.31</v>
+        <v>450970.31</v>
       </c>
     </row>
     <row r="12">
@@ -895,7 +895,7 @@
         <v>1036.17</v>
       </c>
       <c r="J12" t="n">
-        <v>1328887.68</v>
+        <v>438859.68</v>
       </c>
     </row>
     <row r="13">
@@ -933,7 +933,7 @@
         <v>1341.6</v>
       </c>
       <c r="J13" t="n">
-        <v>1429098.01</v>
+        <v>539070.01</v>
       </c>
     </row>
   </sheetData>

--- a/dc2_milk_run_routes.xlsx
+++ b/dc2_milk_run_routes.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DPI66387 -&gt; DPI70316 -&gt; DPI64216 -&gt; DFT80088 -&gt; DPI64413 -&gt; DPI70096 -&gt; DPI64037 -&gt; DPI66172 -&gt; DPI64057 -&gt; DPI63802 -&gt; DPI66051 -&gt; DPI64169 -&gt; DPI66715</t>
+          <t>DPI66339 -&gt; DFT80044 -&gt; DPI64216 -&gt; DFT80088 -&gt; DPI64413 -&gt; DPI70096 -&gt; DPI64037 -&gt; DPI66172 -&gt; DPI64057 -&gt; DPI63802 -&gt; DPI66051 -&gt; DPI64169 -&gt; DPI66715</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -512,10 +512,10 @@
         <v>99.18000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>916.47</v>
+        <v>907.39</v>
       </c>
       <c r="J2" t="n">
-        <v>399584.88</v>
+        <v>396606.2</v>
       </c>
     </row>
     <row r="3">
@@ -531,14 +531,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DPI66658 -&gt; DPI67148 -&gt; DPI64742 -&gt; DPI63976 -&gt; DPI70296 -&gt; DPI67180 -&gt; DPI64634 -&gt; DPI67224 -&gt; DPI66209</t>
+          <t>DPI67148 -&gt; DPI64742 -&gt; DPI63976 -&gt; DPI70296 -&gt; DPI67180 -&gt; DPI64634 -&gt; DPI67224 -&gt; DPI66209 -&gt; DPI66636</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="F3" t="n">
         <v>1613</v>
@@ -547,13 +547,13 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>99.90000000000001</v>
+        <v>99.69</v>
       </c>
       <c r="I3" t="n">
-        <v>983.55</v>
+        <v>985.9400000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>421596.09</v>
+        <v>422378.22</v>
       </c>
     </row>
     <row r="4">
@@ -607,14 +607,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DPI64052 -&gt; DPI67187 -&gt; DPI64666 -&gt; DPI70190 -&gt; DPI70253 -&gt; DPI64056 -&gt; DPI67074 -&gt; DPI64628 -&gt; DPI64119 -&gt; DPI66636</t>
+          <t>DPI70142 -&gt; DPI66069 -&gt; DPI64686 -&gt; DPI70255 -&gt; DPI66645 -&gt; DPI64244 -&gt; DPI66128 -&gt; DPI64094</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="F5" t="n">
         <v>1613</v>
@@ -623,13 +623,13 @@
         <v>980</v>
       </c>
       <c r="H5" t="n">
-        <v>97.55</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>1065.26</v>
+        <v>611.55</v>
       </c>
       <c r="J5" t="n">
-        <v>448403.88</v>
+        <v>299542.34</v>
       </c>
     </row>
     <row r="6">
@@ -645,14 +645,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPI64431 -&gt; DPI66449 -&gt; DPI67072 -&gt; DPI66153 -&gt; DPI66154 -&gt; DPI66373 -&gt; DPI64196 -&gt; DPI66221 -&gt; DPI66597</t>
+          <t>DPI66597 -&gt; DPI66373 -&gt; DPI66154 -&gt; DPI64592 -&gt; DPI66449 -&gt; DPI67072 -&gt; DPI66153 -&gt; DPI64196 -&gt; DPI66221</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>957</v>
+        <v>975</v>
       </c>
       <c r="F6" t="n">
         <v>1613</v>
@@ -661,13 +661,13 @@
         <v>980</v>
       </c>
       <c r="H6" t="n">
-        <v>97.65000000000001</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>529.26</v>
+        <v>455.72</v>
       </c>
       <c r="J6" t="n">
-        <v>272542.49</v>
+        <v>248412.78</v>
       </c>
     </row>
     <row r="7">
@@ -683,11 +683,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPI66069 -&gt; DPI64039 -&gt; DPI66289 -&gt; DPI66203 -&gt; DPI66574 -&gt; DPI66078 -&gt; DPI64433 -&gt; DPI64480</t>
+          <t>DPI66179 -&gt; DPI64218 -&gt; DPI64039 -&gt; DPI66289 -&gt; DPI66203 -&gt; DPI66574 -&gt; DPI66078 -&gt; DPI64433 -&gt; DPI64480</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>969</v>
@@ -702,10 +702,10 @@
         <v>98.88</v>
       </c>
       <c r="I7" t="n">
-        <v>976.47</v>
+        <v>979.24</v>
       </c>
       <c r="J7" t="n">
-        <v>419271.2</v>
+        <v>420179.55</v>
       </c>
     </row>
     <row r="8">
@@ -721,7 +721,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPI64436 -&gt; DPI64456 -&gt; DPI66946 -&gt; DPI64136 -&gt; DPI67121 -&gt; DPI66039 -&gt; DPI66307 -&gt; DPI64638 -&gt; DPI63958</t>
+          <t>DPI63958 -&gt; DPI64638 -&gt; DPI66307 -&gt; DPI66039 -&gt; DPI67121 -&gt; DPI64136 -&gt; DPI66946 -&gt; DPI64456 -&gt; DPI64436</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -759,14 +759,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DPI66179 -&gt; DPI64218 -&gt; DPI64301 -&gt; DPI70255 -&gt; DPI66645 -&gt; DPI64244 -&gt; DPI66128 -&gt; DPI64094 -&gt; DPI70142</t>
+          <t>DPI70009 -&gt; DPI66742 -&gt; DPI67178 -&gt; DPI64724 -&gt; DPI63915 -&gt; DPI64297 -&gt; DPI66067 -&gt; DPI70213 -&gt; DPI70105</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>962</v>
+        <v>978</v>
       </c>
       <c r="F9" t="n">
         <v>1613</v>
@@ -775,13 +775,13 @@
         <v>980</v>
       </c>
       <c r="H9" t="n">
-        <v>98.16</v>
+        <v>99.8</v>
       </c>
       <c r="I9" t="n">
-        <v>613.0599999999999</v>
+        <v>994.71</v>
       </c>
       <c r="J9" t="n">
-        <v>300038.08</v>
+        <v>425254.88</v>
       </c>
     </row>
     <row r="10">
@@ -797,14 +797,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DPI70009 -&gt; DPI63827 -&gt; DPI66313 -&gt; DPI66576 -&gt; DPI64592 -&gt; DPI63919 -&gt; DPI66679 -&gt; DPI70047 -&gt; DPI66923 -&gt; DFT80078</t>
+          <t>DPI66923 -&gt; DPI66658 -&gt; DPI70047 -&gt; DPI66679 -&gt; DPI64431 -&gt; DPI63919 -&gt; DPI70081 -&gt; DPI66576 -&gt; DPI66313 -&gt; DPI63827</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="F10" t="n">
         <v>1613</v>
@@ -813,13 +813,13 @@
         <v>980</v>
       </c>
       <c r="H10" t="n">
-        <v>98.47</v>
+        <v>99.69</v>
       </c>
       <c r="I10" t="n">
-        <v>1113.51</v>
+        <v>1004.88</v>
       </c>
       <c r="J10" t="n">
-        <v>464235.26</v>
+        <v>428593.16</v>
       </c>
     </row>
     <row r="11">
@@ -835,14 +835,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DPI70081 -&gt; DPI64624 -&gt; DPI66102 -&gt; DPI64166 -&gt; DPI66384 -&gt; DPI66408 -&gt; DPI64392 -&gt; DPI66618 -&gt; DPI66653</t>
+          <t>DPI64052 -&gt; DPI67187 -&gt; DFT80077 -&gt; DPI64666 -&gt; DPI70190 -&gt; DPI70253 -&gt; DPI64056 -&gt; DPI67074 -&gt; DPI64628 -&gt; DPI64119 -&gt; DFT80078</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>979</v>
+        <v>969</v>
       </c>
       <c r="F11" t="n">
         <v>1613</v>
@@ -851,13 +851,13 @@
         <v>980</v>
       </c>
       <c r="H11" t="n">
-        <v>99.90000000000001</v>
+        <v>98.88</v>
       </c>
       <c r="I11" t="n">
-        <v>1073.08</v>
+        <v>1104.26</v>
       </c>
       <c r="J11" t="n">
-        <v>450970.31</v>
+        <v>461199.37</v>
       </c>
     </row>
     <row r="12">
@@ -873,14 +873,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DPI67178 -&gt; DPI64297 -&gt; DPI63915 -&gt; DPI64724 -&gt; DPI66742 -&gt; DPI66067 -&gt; DPI70213 -&gt; DPI70105 -&gt; DFT80077</t>
+          <t>DPI64450 -&gt; DPI66387 -&gt; DPI64301 -&gt; DPI66590 -&gt; DPI70316 -&gt; DPI66096 -&gt; DPI64018 -&gt; DPI66736 -&gt; DPI70229</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="F12" t="n">
         <v>1613</v>
@@ -889,13 +889,13 @@
         <v>980</v>
       </c>
       <c r="H12" t="n">
-        <v>98.47</v>
+        <v>98.78</v>
       </c>
       <c r="I12" t="n">
-        <v>1036.17</v>
+        <v>1343.97</v>
       </c>
       <c r="J12" t="n">
-        <v>438859.68</v>
+        <v>539849.98</v>
       </c>
     </row>
     <row r="13">
@@ -911,14 +911,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DPI64450 -&gt; DPI64686 -&gt; DPI66339 -&gt; DPI66590 -&gt; DFT80044 -&gt; DPI66096 -&gt; DPI64018 -&gt; DPI70229 -&gt; DPI66736</t>
+          <t>DPI66653 -&gt; DPI64624 -&gt; DPI66102 -&gt; DPI64166 -&gt; DPI66384 -&gt; DPI64392 -&gt; DPI66408 -&gt; DPI66618</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>966</v>
+        <v>925</v>
       </c>
       <c r="F13" t="n">
         <v>1613</v>
@@ -927,13 +927,13 @@
         <v>980</v>
       </c>
       <c r="H13" t="n">
-        <v>98.56999999999999</v>
+        <v>94.39</v>
       </c>
       <c r="I13" t="n">
-        <v>1341.6</v>
+        <v>1070.13</v>
       </c>
       <c r="J13" t="n">
-        <v>539070.01</v>
+        <v>450001.99</v>
       </c>
     </row>
   </sheetData>

--- a/dc2_milk_run_routes.xlsx
+++ b/dc2_milk_run_routes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,16 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>fixed_cost</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>variable_cost_per_km</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>monthly_cost</t>
         </is>
       </c>
@@ -493,14 +503,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DPI66339 -&gt; DFT80044 -&gt; DPI64216 -&gt; DFT80088 -&gt; DPI64413 -&gt; DPI70096 -&gt; DPI64037 -&gt; DPI66172 -&gt; DPI64057 -&gt; DPI63802 -&gt; DPI66051 -&gt; DPI64169 -&gt; DPI66715</t>
+          <t>DPI64218 -&gt; DPI66289 -&gt; DPI64039 -&gt; DPI66069 -&gt; DPI70255 -&gt; DPI66645 -&gt; DPI64413 -&gt; DPI64244 -&gt; DFT80088 -&gt; DPI64216 -&gt; DPI70316</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>972</v>
+        <v>926</v>
       </c>
       <c r="F2" t="n">
         <v>1613</v>
@@ -509,13 +519,19 @@
         <v>980</v>
       </c>
       <c r="H2" t="n">
-        <v>99.18000000000001</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>907.39</v>
+        <v>595.22</v>
       </c>
       <c r="J2" t="n">
-        <v>396606.2</v>
+        <v>98892</v>
+      </c>
+      <c r="K2" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="L2" t="n">
+        <v>294185.11</v>
       </c>
     </row>
     <row r="3">
@@ -531,14 +547,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DPI67148 -&gt; DPI64742 -&gt; DPI63976 -&gt; DPI70296 -&gt; DPI67180 -&gt; DPI64634 -&gt; DPI67224 -&gt; DPI66209 -&gt; DPI66636</t>
+          <t>DPI66658 -&gt; DPI67148 -&gt; DPI64742 -&gt; DPI63976 -&gt; DPI70296 -&gt; DPI67180 -&gt; DPI64634 -&gt; DPI67224 -&gt; DPI66209</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="F3" t="n">
         <v>1613</v>
@@ -547,13 +563,19 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>99.69</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>985.9400000000001</v>
+        <v>983.55</v>
       </c>
       <c r="J3" t="n">
-        <v>422378.22</v>
+        <v>98892</v>
+      </c>
+      <c r="K3" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="L3" t="n">
+        <v>421596.09</v>
       </c>
     </row>
     <row r="4">
@@ -591,6 +613,12 @@
         <v>1399.26</v>
       </c>
       <c r="J4" t="n">
+        <v>98892</v>
+      </c>
+      <c r="K4" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="L4" t="n">
         <v>557988.3</v>
       </c>
     </row>
@@ -607,14 +635,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DPI70142 -&gt; DPI66069 -&gt; DPI64686 -&gt; DPI70255 -&gt; DPI66645 -&gt; DPI64244 -&gt; DPI66128 -&gt; DPI64094</t>
+          <t>DPI64052 -&gt; DPI66179 -&gt; DPI66597 -&gt; DPI63958 -&gt; DPI66039 -&gt; DPI66307 -&gt; DPI64638</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>960</v>
+        <v>865</v>
       </c>
       <c r="F5" t="n">
         <v>1613</v>
@@ -623,13 +651,19 @@
         <v>980</v>
       </c>
       <c r="H5" t="n">
-        <v>97.95999999999999</v>
+        <v>88.27</v>
       </c>
       <c r="I5" t="n">
-        <v>611.55</v>
+        <v>204.96</v>
       </c>
       <c r="J5" t="n">
-        <v>299542.34</v>
+        <v>98892</v>
+      </c>
+      <c r="K5" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="L5" t="n">
+        <v>166140.82</v>
       </c>
     </row>
     <row r="6">
@@ -645,14 +679,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPI66597 -&gt; DPI66373 -&gt; DPI66154 -&gt; DPI64592 -&gt; DPI66449 -&gt; DPI67072 -&gt; DPI66153 -&gt; DPI64196 -&gt; DPI66221</t>
+          <t>DPI70009 -&gt; DPI63827 -&gt; DPI66313 -&gt; DPI66576 -&gt; DPI64592 -&gt; DPI63919 -&gt; DPI66679 -&gt; DPI70047</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>975</v>
+        <v>854</v>
       </c>
       <c r="F6" t="n">
         <v>1613</v>
@@ -661,13 +695,19 @@
         <v>980</v>
       </c>
       <c r="H6" t="n">
-        <v>99.48999999999999</v>
+        <v>87.14</v>
       </c>
       <c r="I6" t="n">
-        <v>455.72</v>
+        <v>708.0700000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>248412.78</v>
+        <v>98892</v>
+      </c>
+      <c r="K6" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="L6" t="n">
+        <v>331208.44</v>
       </c>
     </row>
     <row r="7">
@@ -683,14 +723,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPI66179 -&gt; DPI64218 -&gt; DPI64039 -&gt; DPI66289 -&gt; DPI66203 -&gt; DPI66574 -&gt; DPI66078 -&gt; DPI64433 -&gt; DPI64480</t>
+          <t>DPI64094 -&gt; DPI66128 -&gt; DPI70096 -&gt; DPI64037 -&gt; DPI66172 -&gt; DPI64057 -&gt; DPI63802 -&gt; DPI66051 -&gt; DPI64169 -&gt; DPI66715</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>969</v>
+        <v>925</v>
       </c>
       <c r="F7" t="n">
         <v>1613</v>
@@ -699,13 +739,19 @@
         <v>980</v>
       </c>
       <c r="H7" t="n">
-        <v>98.88</v>
+        <v>94.39</v>
       </c>
       <c r="I7" t="n">
-        <v>979.24</v>
+        <v>920.26</v>
       </c>
       <c r="J7" t="n">
-        <v>420179.55</v>
+        <v>98892</v>
+      </c>
+      <c r="K7" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="L7" t="n">
+        <v>400828.8</v>
       </c>
     </row>
     <row r="8">
@@ -721,14 +767,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPI63958 -&gt; DPI64638 -&gt; DPI66307 -&gt; DPI66039 -&gt; DPI67121 -&gt; DPI64136 -&gt; DPI66946 -&gt; DPI64456 -&gt; DPI64436</t>
+          <t>DPI66653 -&gt; DPI66449 -&gt; DPI67072 -&gt; DPI66153 -&gt; DPI70081 -&gt; DPI66154 -&gt; DPI66373 -&gt; DPI66221</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>961</v>
+        <v>871</v>
       </c>
       <c r="F8" t="n">
         <v>1613</v>
@@ -737,13 +783,19 @@
         <v>980</v>
       </c>
       <c r="H8" t="n">
-        <v>98.06</v>
+        <v>88.88</v>
       </c>
       <c r="I8" t="n">
-        <v>919.02</v>
+        <v>426.58</v>
       </c>
       <c r="J8" t="n">
-        <v>400421.92</v>
+        <v>98892</v>
+      </c>
+      <c r="K8" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="L8" t="n">
+        <v>238853.93</v>
       </c>
     </row>
     <row r="9">
@@ -759,14 +811,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DPI70009 -&gt; DPI66742 -&gt; DPI67178 -&gt; DPI64724 -&gt; DPI63915 -&gt; DPI64297 -&gt; DPI66067 -&gt; DPI70213 -&gt; DPI70105</t>
+          <t>DPI64480 -&gt; DPI66078 -&gt; DPI64433 -&gt; DPI67187 -&gt; DPI70105 -&gt; DPI64436 -&gt; DPI64456 -&gt; DPI66946 -&gt; DPI66574</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>978</v>
+        <v>963</v>
       </c>
       <c r="F9" t="n">
         <v>1613</v>
@@ -775,13 +827,19 @@
         <v>980</v>
       </c>
       <c r="H9" t="n">
-        <v>99.8</v>
+        <v>98.27</v>
       </c>
       <c r="I9" t="n">
-        <v>994.71</v>
+        <v>874.7</v>
       </c>
       <c r="J9" t="n">
-        <v>425254.88</v>
+        <v>98892</v>
+      </c>
+      <c r="K9" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="L9" t="n">
+        <v>385882.65</v>
       </c>
     </row>
     <row r="10">
@@ -797,14 +855,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DPI66923 -&gt; DPI66658 -&gt; DPI70047 -&gt; DPI66679 -&gt; DPI64431 -&gt; DPI63919 -&gt; DPI70081 -&gt; DPI66576 -&gt; DPI66313 -&gt; DPI63827</t>
+          <t>DPI67121 -&gt; DPI64450 -&gt; DPI64686 -&gt; DPI66203 -&gt; DPI64301 -&gt; DFT80044 -&gt; DPI66590 -&gt; DPI66339 -&gt; DPI66387</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>977</v>
+        <v>957</v>
       </c>
       <c r="F10" t="n">
         <v>1613</v>
@@ -813,13 +871,19 @@
         <v>980</v>
       </c>
       <c r="H10" t="n">
-        <v>99.69</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>1004.88</v>
+        <v>222.61</v>
       </c>
       <c r="J10" t="n">
-        <v>428593.16</v>
+        <v>98892</v>
+      </c>
+      <c r="K10" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="L10" t="n">
+        <v>171928.75</v>
       </c>
     </row>
     <row r="11">
@@ -835,14 +899,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DPI64052 -&gt; DPI67187 -&gt; DFT80077 -&gt; DPI64666 -&gt; DPI70190 -&gt; DPI70253 -&gt; DPI64056 -&gt; DPI67074 -&gt; DPI64628 -&gt; DPI64119 -&gt; DFT80078</t>
+          <t>DPI70142 -&gt; DPI66742 -&gt; DPI63915 -&gt; DPI64724 -&gt; DPI67178 -&gt; DPI64297 -&gt; DPI66067 -&gt; DPI70213 -&gt; DPI64136</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>969</v>
+        <v>978</v>
       </c>
       <c r="F11" t="n">
         <v>1613</v>
@@ -851,13 +915,19 @@
         <v>980</v>
       </c>
       <c r="H11" t="n">
-        <v>98.88</v>
+        <v>99.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1104.26</v>
+        <v>855.61</v>
       </c>
       <c r="J11" t="n">
-        <v>461199.37</v>
+        <v>98892</v>
+      </c>
+      <c r="K11" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="L11" t="n">
+        <v>379616.42</v>
       </c>
     </row>
     <row r="12">
@@ -873,29 +943,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DPI64450 -&gt; DPI66387 -&gt; DPI64301 -&gt; DPI66590 -&gt; DPI70316 -&gt; DPI66096 -&gt; DPI64018 -&gt; DPI66736 -&gt; DPI70229</t>
+          <t>DPI66736 -&gt; DPI70229 -&gt; DPI64018 -&gt; DPI66096</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>968</v>
+        <v>520</v>
       </c>
       <c r="F12" t="n">
-        <v>1613</v>
+        <v>1109</v>
       </c>
       <c r="G12" t="n">
-        <v>980</v>
+        <v>660</v>
       </c>
       <c r="H12" t="n">
-        <v>98.78</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>1343.97</v>
+        <v>1183.99</v>
       </c>
       <c r="J12" t="n">
-        <v>539849.98</v>
+        <v>86100</v>
+      </c>
+      <c r="K12" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="L12" t="n">
+        <v>423299.77</v>
       </c>
     </row>
     <row r="13">
@@ -911,14 +987,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DPI66653 -&gt; DPI64624 -&gt; DPI66102 -&gt; DPI64166 -&gt; DPI66384 -&gt; DPI64392 -&gt; DPI66408 -&gt; DPI66618</t>
+          <t>DPI64196 -&gt; DPI64624 -&gt; DPI66102 -&gt; DPI64166 -&gt; DPI66384 -&gt; DPI66408 -&gt; DPI64392 -&gt; DPI66618 -&gt; DPI64431</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>925</v>
+        <v>974</v>
       </c>
       <c r="F13" t="n">
         <v>1613</v>
@@ -927,13 +1003,63 @@
         <v>980</v>
       </c>
       <c r="H13" t="n">
-        <v>94.39</v>
+        <v>99.39</v>
       </c>
       <c r="I13" t="n">
-        <v>1070.13</v>
+        <v>1068.39</v>
       </c>
       <c r="J13" t="n">
-        <v>450001.99</v>
+        <v>98892</v>
+      </c>
+      <c r="K13" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="L13" t="n">
+        <v>449432.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DC_2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DPI66923 -&gt; DFT80077 -&gt; DPI66636 -&gt; DPI64666 -&gt; DPI70190 -&gt; DPI70253 -&gt; DPI64056 -&gt; DPI67074 -&gt; DPI64628 -&gt; DPI64119 -&gt; DFT80078</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E14" t="n">
+        <v>819</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1613</v>
+      </c>
+      <c r="G14" t="n">
+        <v>980</v>
+      </c>
+      <c r="H14" t="n">
+        <v>83.56999999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>939.01</v>
+      </c>
+      <c r="J14" t="n">
+        <v>98892</v>
+      </c>
+      <c r="K14" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="L14" t="n">
+        <v>406981.88</v>
       </c>
     </row>
   </sheetData>

--- a/dc2_milk_run_routes.xlsx
+++ b/dc2_milk_run_routes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,14 +503,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DPI64218 -&gt; DPI66289 -&gt; DPI64039 -&gt; DPI66069 -&gt; DPI70255 -&gt; DPI66645 -&gt; DPI64413 -&gt; DPI64244 -&gt; DFT80088 -&gt; DPI64216 -&gt; DPI70316</t>
+          <t>DPI66387 -&gt; DPI70316 -&gt; DPI64216 -&gt; DFT80088 -&gt; DPI64413 -&gt; DPI70096 -&gt; DPI64037 -&gt; DPI66172 -&gt; DPI64057 -&gt; DPI63802 -&gt; DPI66051 -&gt; DPI64169 -&gt; DPI66715</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>926</v>
+        <v>972</v>
       </c>
       <c r="F2" t="n">
         <v>1613</v>
@@ -519,10 +519,10 @@
         <v>980</v>
       </c>
       <c r="H2" t="n">
-        <v>94.48999999999999</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>595.22</v>
+        <v>916.47</v>
       </c>
       <c r="J2" t="n">
         <v>98892</v>
@@ -531,7 +531,7 @@
         <v>32.81</v>
       </c>
       <c r="L2" t="n">
-        <v>294185.11</v>
+        <v>399584.88</v>
       </c>
     </row>
     <row r="3">
@@ -635,14 +635,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DPI64052 -&gt; DPI66179 -&gt; DPI66597 -&gt; DPI63958 -&gt; DPI66039 -&gt; DPI66307 -&gt; DPI64638</t>
+          <t>DPI64052 -&gt; DPI67187 -&gt; DPI64666 -&gt; DPI70190 -&gt; DPI70253 -&gt; DPI64056 -&gt; DPI67074 -&gt; DPI64628 -&gt; DPI64119 -&gt; DPI66636</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>865</v>
+        <v>956</v>
       </c>
       <c r="F5" t="n">
         <v>1613</v>
@@ -651,10 +651,10 @@
         <v>980</v>
       </c>
       <c r="H5" t="n">
-        <v>88.27</v>
+        <v>97.55</v>
       </c>
       <c r="I5" t="n">
-        <v>204.96</v>
+        <v>1065.26</v>
       </c>
       <c r="J5" t="n">
         <v>98892</v>
@@ -663,7 +663,7 @@
         <v>32.81</v>
       </c>
       <c r="L5" t="n">
-        <v>166140.82</v>
+        <v>448403.88</v>
       </c>
     </row>
     <row r="6">
@@ -679,14 +679,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPI70009 -&gt; DPI63827 -&gt; DPI66313 -&gt; DPI66576 -&gt; DPI64592 -&gt; DPI63919 -&gt; DPI66679 -&gt; DPI70047</t>
+          <t>DPI64431 -&gt; DPI66449 -&gt; DPI67072 -&gt; DPI66153 -&gt; DPI66154 -&gt; DPI66373 -&gt; DPI64196 -&gt; DPI66221 -&gt; DPI66597</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>854</v>
+        <v>957</v>
       </c>
       <c r="F6" t="n">
         <v>1613</v>
@@ -695,10 +695,10 @@
         <v>980</v>
       </c>
       <c r="H6" t="n">
-        <v>87.14</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>708.0700000000001</v>
+        <v>529.26</v>
       </c>
       <c r="J6" t="n">
         <v>98892</v>
@@ -707,7 +707,7 @@
         <v>32.81</v>
       </c>
       <c r="L6" t="n">
-        <v>331208.44</v>
+        <v>272542.49</v>
       </c>
     </row>
     <row r="7">
@@ -723,14 +723,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPI64094 -&gt; DPI66128 -&gt; DPI70096 -&gt; DPI64037 -&gt; DPI66172 -&gt; DPI64057 -&gt; DPI63802 -&gt; DPI66051 -&gt; DPI64169 -&gt; DPI66715</t>
+          <t>DPI66069 -&gt; DPI64039 -&gt; DPI66289 -&gt; DPI66203 -&gt; DPI66574 -&gt; DPI66078 -&gt; DPI64433 -&gt; DPI64480</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>925</v>
+        <v>969</v>
       </c>
       <c r="F7" t="n">
         <v>1613</v>
@@ -739,10 +739,10 @@
         <v>980</v>
       </c>
       <c r="H7" t="n">
-        <v>94.39</v>
+        <v>98.88</v>
       </c>
       <c r="I7" t="n">
-        <v>920.26</v>
+        <v>976.47</v>
       </c>
       <c r="J7" t="n">
         <v>98892</v>
@@ -751,7 +751,7 @@
         <v>32.81</v>
       </c>
       <c r="L7" t="n">
-        <v>400828.8</v>
+        <v>419271.2</v>
       </c>
     </row>
     <row r="8">
@@ -767,14 +767,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPI66653 -&gt; DPI66449 -&gt; DPI67072 -&gt; DPI66153 -&gt; DPI70081 -&gt; DPI66154 -&gt; DPI66373 -&gt; DPI66221</t>
+          <t>DPI64436 -&gt; DPI64456 -&gt; DPI66946 -&gt; DPI64136 -&gt; DPI67121 -&gt; DPI66039 -&gt; DPI66307 -&gt; DPI64638 -&gt; DPI63958</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>871</v>
+        <v>961</v>
       </c>
       <c r="F8" t="n">
         <v>1613</v>
@@ -783,10 +783,10 @@
         <v>980</v>
       </c>
       <c r="H8" t="n">
-        <v>88.88</v>
+        <v>98.06</v>
       </c>
       <c r="I8" t="n">
-        <v>426.58</v>
+        <v>919.02</v>
       </c>
       <c r="J8" t="n">
         <v>98892</v>
@@ -795,7 +795,7 @@
         <v>32.81</v>
       </c>
       <c r="L8" t="n">
-        <v>238853.93</v>
+        <v>400421.92</v>
       </c>
     </row>
     <row r="9">
@@ -811,14 +811,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DPI64480 -&gt; DPI66078 -&gt; DPI64433 -&gt; DPI67187 -&gt; DPI70105 -&gt; DPI64436 -&gt; DPI64456 -&gt; DPI66946 -&gt; DPI66574</t>
+          <t>DPI66179 -&gt; DPI64218 -&gt; DPI64301 -&gt; DPI70255 -&gt; DPI66645 -&gt; DPI64244 -&gt; DPI66128 -&gt; DPI64094 -&gt; DPI70142</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="F9" t="n">
         <v>1613</v>
@@ -827,10 +827,10 @@
         <v>980</v>
       </c>
       <c r="H9" t="n">
-        <v>98.27</v>
+        <v>98.16</v>
       </c>
       <c r="I9" t="n">
-        <v>874.7</v>
+        <v>613.0599999999999</v>
       </c>
       <c r="J9" t="n">
         <v>98892</v>
@@ -839,7 +839,7 @@
         <v>32.81</v>
       </c>
       <c r="L9" t="n">
-        <v>385882.65</v>
+        <v>300038.08</v>
       </c>
     </row>
     <row r="10">
@@ -855,14 +855,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DPI67121 -&gt; DPI64450 -&gt; DPI64686 -&gt; DPI66203 -&gt; DPI64301 -&gt; DFT80044 -&gt; DPI66590 -&gt; DPI66339 -&gt; DPI66387</t>
+          <t>DPI70009 -&gt; DPI63827 -&gt; DPI66313 -&gt; DPI66576 -&gt; DPI64592 -&gt; DPI63919 -&gt; DPI66679 -&gt; DPI70047 -&gt; DPI66923 -&gt; DFT80078</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="F10" t="n">
         <v>1613</v>
@@ -871,10 +871,10 @@
         <v>980</v>
       </c>
       <c r="H10" t="n">
-        <v>97.65000000000001</v>
+        <v>98.47</v>
       </c>
       <c r="I10" t="n">
-        <v>222.61</v>
+        <v>1113.51</v>
       </c>
       <c r="J10" t="n">
         <v>98892</v>
@@ -883,7 +883,7 @@
         <v>32.81</v>
       </c>
       <c r="L10" t="n">
-        <v>171928.75</v>
+        <v>464235.26</v>
       </c>
     </row>
     <row r="11">
@@ -899,14 +899,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DPI70142 -&gt; DPI66742 -&gt; DPI63915 -&gt; DPI64724 -&gt; DPI67178 -&gt; DPI64297 -&gt; DPI66067 -&gt; DPI70213 -&gt; DPI64136</t>
+          <t>DPI70081 -&gt; DPI64624 -&gt; DPI66102 -&gt; DPI64166 -&gt; DPI66384 -&gt; DPI66408 -&gt; DPI64392 -&gt; DPI66618 -&gt; DPI66653</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="F11" t="n">
         <v>1613</v>
@@ -915,10 +915,10 @@
         <v>980</v>
       </c>
       <c r="H11" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>855.61</v>
+        <v>1073.08</v>
       </c>
       <c r="J11" t="n">
         <v>98892</v>
@@ -927,7 +927,7 @@
         <v>32.81</v>
       </c>
       <c r="L11" t="n">
-        <v>379616.42</v>
+        <v>450970.31</v>
       </c>
     </row>
     <row r="12">
@@ -943,35 +943,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DPI66736 -&gt; DPI70229 -&gt; DPI64018 -&gt; DPI66096</t>
+          <t>DPI67178 -&gt; DPI64297 -&gt; DPI63915 -&gt; DPI64724 -&gt; DPI66742 -&gt; DPI66067 -&gt; DPI70213 -&gt; DPI70105 -&gt; DFT80077</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>520</v>
+        <v>965</v>
       </c>
       <c r="F12" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="G12" t="n">
-        <v>660</v>
+        <v>980</v>
       </c>
       <c r="H12" t="n">
-        <v>78.79000000000001</v>
+        <v>98.47</v>
       </c>
       <c r="I12" t="n">
-        <v>1183.99</v>
+        <v>1036.17</v>
       </c>
       <c r="J12" t="n">
-        <v>86100</v>
+        <v>98892</v>
       </c>
       <c r="K12" t="n">
-        <v>28.48</v>
+        <v>32.81</v>
       </c>
       <c r="L12" t="n">
-        <v>423299.77</v>
+        <v>438859.68</v>
       </c>
     </row>
     <row r="13">
@@ -987,14 +987,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DPI64196 -&gt; DPI64624 -&gt; DPI66102 -&gt; DPI64166 -&gt; DPI66384 -&gt; DPI66408 -&gt; DPI64392 -&gt; DPI66618 -&gt; DPI64431</t>
+          <t>DPI64450 -&gt; DPI64686 -&gt; DPI66339 -&gt; DPI66590 -&gt; DFT80044 -&gt; DPI66096 -&gt; DPI64018 -&gt; DPI70229 -&gt; DPI66736</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="F13" t="n">
         <v>1613</v>
@@ -1003,10 +1003,10 @@
         <v>980</v>
       </c>
       <c r="H13" t="n">
-        <v>99.39</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>1068.39</v>
+        <v>1341.6</v>
       </c>
       <c r="J13" t="n">
         <v>98892</v>
@@ -1015,51 +1015,7 @@
         <v>32.81</v>
       </c>
       <c r="L13" t="n">
-        <v>449432.3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>R13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>DC_2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>DPI66923 -&gt; DFT80077 -&gt; DPI66636 -&gt; DPI64666 -&gt; DPI70190 -&gt; DPI70253 -&gt; DPI64056 -&gt; DPI67074 -&gt; DPI64628 -&gt; DPI64119 -&gt; DFT80078</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11</v>
-      </c>
-      <c r="E14" t="n">
-        <v>819</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1613</v>
-      </c>
-      <c r="G14" t="n">
-        <v>980</v>
-      </c>
-      <c r="H14" t="n">
-        <v>83.56999999999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>939.01</v>
-      </c>
-      <c r="J14" t="n">
-        <v>98892</v>
-      </c>
-      <c r="K14" t="n">
-        <v>32.81</v>
-      </c>
-      <c r="L14" t="n">
-        <v>406981.88</v>
+        <v>539070.01</v>
       </c>
     </row>
   </sheetData>

--- a/dc2_milk_run_routes.xlsx
+++ b/dc2_milk_run_routes.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPI64431 -&gt; DPI66449 -&gt; DPI67072 -&gt; DPI66153 -&gt; DPI66154 -&gt; DPI66373 -&gt; DPI64196 -&gt; DPI66221 -&gt; DPI66597</t>
+          <t>DPI66597 -&gt; DPI66373 -&gt; DPI66154 -&gt; DPI66153 -&gt; DPI67072 -&gt; DPI66449 -&gt; DPI64431 -&gt; DPI64196 -&gt; DPI66221</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -698,7 +698,7 @@
         <v>97.65000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>529.26</v>
+        <v>534.65</v>
       </c>
       <c r="J6" t="n">
         <v>98892</v>
@@ -707,7 +707,7 @@
         <v>32.81</v>
       </c>
       <c r="L6" t="n">
-        <v>272542.49</v>
+        <v>274309.75</v>
       </c>
     </row>
     <row r="7">
@@ -767,7 +767,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPI64436 -&gt; DPI64456 -&gt; DPI66946 -&gt; DPI64136 -&gt; DPI67121 -&gt; DPI66039 -&gt; DPI66307 -&gt; DPI64638 -&gt; DPI63958</t>
+          <t>DPI64638 -&gt; DPI66307 -&gt; DPI66039 -&gt; DPI63958 -&gt; DPI67121 -&gt; DPI64136 -&gt; DPI66946 -&gt; DPI64456 -&gt; DPI64436</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -786,7 +786,7 @@
         <v>98.06</v>
       </c>
       <c r="I8" t="n">
-        <v>919.02</v>
+        <v>919.88</v>
       </c>
       <c r="J8" t="n">
         <v>98892</v>
@@ -795,7 +795,7 @@
         <v>32.81</v>
       </c>
       <c r="L8" t="n">
-        <v>400421.92</v>
+        <v>400704.79</v>
       </c>
     </row>
     <row r="9">
@@ -943,7 +943,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DPI67178 -&gt; DPI64297 -&gt; DPI63915 -&gt; DPI64724 -&gt; DPI66742 -&gt; DPI66067 -&gt; DPI70213 -&gt; DPI70105 -&gt; DFT80077</t>
+          <t>DPI66742 -&gt; DPI64724 -&gt; DPI63915 -&gt; DPI64297 -&gt; DPI67178 -&gt; DPI66067 -&gt; DPI70213 -&gt; DPI70105 -&gt; DFT80077</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -962,7 +962,7 @@
         <v>98.47</v>
       </c>
       <c r="I12" t="n">
-        <v>1036.17</v>
+        <v>1035.78</v>
       </c>
       <c r="J12" t="n">
         <v>98892</v>
@@ -971,7 +971,7 @@
         <v>32.81</v>
       </c>
       <c r="L12" t="n">
-        <v>438859.68</v>
+        <v>438730.97</v>
       </c>
     </row>
     <row r="13">
